--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260930.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260930.xlsx
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>202610TX</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>興富發</t>
+          <t>台指期</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>79,790,000</t>
+          <t>320</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>202610TX</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>台指期</t>
+          <t>興富發</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>79,790,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
